--- a/artfynd/A 10006-2021 artfynd.xlsx
+++ b/artfynd/A 10006-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711272</v>
+        <v>113711271</v>
       </c>
       <c r="B2" t="n">
         <v>79265</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647370</v>
+        <v>647283</v>
       </c>
       <c r="R2" t="n">
-        <v>7036763</v>
+        <v>7036800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711271</v>
+        <v>113711270</v>
       </c>
       <c r="B3" t="n">
         <v>79265</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647283</v>
+        <v>647330</v>
       </c>
       <c r="R3" t="n">
-        <v>7036800</v>
+        <v>7036740</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711270</v>
+        <v>113711272</v>
       </c>
       <c r="B4" t="n">
         <v>79265</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647330</v>
+        <v>647370</v>
       </c>
       <c r="R4" t="n">
-        <v>7036740</v>
+        <v>7036763</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 10006-2021 artfynd.xlsx
+++ b/artfynd/A 10006-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711271</v>
+        <v>113711270</v>
       </c>
       <c r="B2" t="n">
         <v>79265</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647283</v>
+        <v>647330</v>
       </c>
       <c r="R2" t="n">
-        <v>7036800</v>
+        <v>7036740</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711270</v>
+        <v>113711271</v>
       </c>
       <c r="B3" t="n">
         <v>79265</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647330</v>
+        <v>647283</v>
       </c>
       <c r="R3" t="n">
-        <v>7036740</v>
+        <v>7036800</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 10006-2021 artfynd.xlsx
+++ b/artfynd/A 10006-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711270</v>
+        <v>113711272</v>
       </c>
       <c r="B2" t="n">
         <v>79265</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647330</v>
+        <v>647370</v>
       </c>
       <c r="R2" t="n">
-        <v>7036740</v>
+        <v>7036763</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711272</v>
+        <v>113711270</v>
       </c>
       <c r="B4" t="n">
         <v>79265</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647370</v>
+        <v>647330</v>
       </c>
       <c r="R4" t="n">
-        <v>7036763</v>
+        <v>7036740</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 10006-2021 artfynd.xlsx
+++ b/artfynd/A 10006-2021 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113711271</v>
+        <v>113711270</v>
       </c>
       <c r="B3" t="n">
         <v>79265</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>647283</v>
+        <v>647330</v>
       </c>
       <c r="R3" t="n">
-        <v>7036800</v>
+        <v>7036740</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711270</v>
+        <v>113711271</v>
       </c>
       <c r="B4" t="n">
         <v>79265</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647330</v>
+        <v>647283</v>
       </c>
       <c r="R4" t="n">
-        <v>7036740</v>
+        <v>7036800</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 10006-2021 artfynd.xlsx
+++ b/artfynd/A 10006-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113711272</v>
+        <v>113711271</v>
       </c>
       <c r="B2" t="n">
         <v>79265</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647370</v>
+        <v>647283</v>
       </c>
       <c r="R2" t="n">
-        <v>7036763</v>
+        <v>7036800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113711271</v>
+        <v>113711272</v>
       </c>
       <c r="B4" t="n">
         <v>79265</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647283</v>
+        <v>647370</v>
       </c>
       <c r="R4" t="n">
-        <v>7036800</v>
+        <v>7036763</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 10006-2021 artfynd.xlsx
+++ b/artfynd/A 10006-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
